--- a/limerick_pipeline/supply/Limerick_Refused_Withdrawn_Sites.xlsx
+++ b/limerick_pipeline/supply/Limerick_Refused_Withdrawn_Sites.xlsx
@@ -3379,7 +3379,7 @@
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Part 8 - 1201358, 218012</t>
+          <t>218012</t>
         </is>
       </c>
       <c r="O42" s="2" t="n">
